--- a/resampling/input/accessibility_reports_generated/ACF_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/ACF_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O95" headerRowCount="1">
-  <autoFilter ref="A1:O95"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P105" headerRowCount="1">
+  <autoFilter ref="A1:P105"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 130 wards, 94 clusters</t>
+          <t>Assigned to you: 130 wards, 104 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -1853,10 +1864,10 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1879,7 +1890,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rimawa</t>
+          <t>Shinaka</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1890,7 +1901,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gada; Isa; Sabon Birni</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1899,13 +1910,13 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1928,7 +1939,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sabon Gari Dole</t>
+          <t>Rimawa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1939,7 +1950,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Isa; Rabah; Wurno</t>
+          <t>Gada; Isa; Sabon Birni</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1948,13 +1959,13 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1977,7 +1988,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kwakwazo</t>
+          <t>Sabon Gari Dole</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1988,7 +1999,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gada</t>
+          <t>Isa; Rabah; Wurno</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1997,13 +2008,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -2026,7 +2037,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Takakume</t>
+          <t>Kwakwazo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2046,13 +2057,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -2075,7 +2086,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Birjingo</t>
+          <t>Takakume</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2095,13 +2106,13 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2124,7 +2135,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kojiyo</t>
+          <t>Birjingo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2135,7 +2146,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2173,7 +2184,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boyekai</t>
+          <t>Kojiyo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2184,7 +2195,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gada; Gwadabawa</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2193,13 +2204,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2222,7 +2233,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chacho-Marnona</t>
+          <t>Boyekai</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2233,7 +2244,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rabah; Wurno</t>
+          <t>Gada; Gwadabawa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2271,7 +2282,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gandi 2</t>
+          <t>Chacho-Marnona</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2282,7 +2293,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Isa; Rabah</t>
+          <t>Rabah; Wurno</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2320,7 +2331,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gilbadi</t>
+          <t>Gandi 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2331,7 +2342,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gada; Sabon Birni</t>
+          <t>Isa; Rabah</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2369,7 +2380,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Giyawa</t>
+          <t>Gilbadi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2380,7 +2391,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gwadabawa; Wurno</t>
+          <t>Gada; Sabon Birni</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2389,7 +2400,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2418,7 +2429,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Huchi</t>
+          <t>Giyawa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2438,7 +2449,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2467,7 +2478,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kaddi</t>
+          <t>Huchi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2478,7 +2489,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gada</t>
+          <t>Gwadabawa; Wurno</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2516,7 +2527,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Kaddi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2527,7 +2538,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wurno</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2536,10 +2547,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2565,7 +2576,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kiri</t>
+          <t>Kagara</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2576,7 +2587,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gada; Gwadabawa; Illela</t>
+          <t>Wurno</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2585,10 +2596,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2614,7 +2625,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Kiri</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2625,7 +2636,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Gada; Gwadabawa; Illela</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2663,7 +2674,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kwargaba</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2674,7 +2685,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wurno</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2712,7 +2723,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kwarma</t>
+          <t>Kwargaba</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2723,7 +2734,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gada</t>
+          <t>Wurno</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2761,7 +2772,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mammande</t>
+          <t>Kwarma</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2772,7 +2783,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gada; Gwadabawa; Illela</t>
+          <t>Gada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2810,7 +2821,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shinaka</t>
+          <t>Mammande</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2821,7 +2832,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gada</t>
+          <t>Gada; Gwadabawa; Illela</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2833,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4378,33 +4389,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rarah</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Dange-Shuni</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -4427,7 +4430,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -4438,7 +4441,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goronyo</t>
+          <t>Wurno</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4447,13 +4450,13 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -4476,7 +4479,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Maikujera</t>
+          <t>Rarah</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -4487,7 +4490,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kware</t>
+          <t>Dange-Shuni</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4496,13 +4499,13 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -4525,7 +4528,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tsamiya</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -4536,7 +4539,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dange-Shuni; Tureta</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4545,13 +4548,13 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
@@ -4574,25 +4577,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Goddodi</t>
+          <t>Maikujera</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kware</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -4615,7 +4626,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Tsamiya</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -4626,7 +4637,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wurno</t>
+          <t>Dange-Shuni; Tureta</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4635,13 +4646,13 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
@@ -4664,7 +4675,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yarstakuwa</t>
+          <t>Goddodi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -4676,13 +4687,13 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -4705,7 +4716,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gandi 1</t>
+          <t>Yarstakuwa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -4717,13 +4728,13 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -5637,7 +5648,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bagida</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -5648,7 +5659,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kebbe</t>
+          <t>Gwadabawa; Kebbe; Kware; Sabon Birni; Tangaza</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5657,13 +5668,13 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -5686,7 +5697,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sabon Birni</t>
+          <t>Bagida</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -5697,7 +5708,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gwadabawa; Kebbe; Kware; Sabon Birni; Tangaza</t>
+          <t>Kebbe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5706,13 +5717,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
@@ -7038,7 +7049,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O131" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7054,7 +7065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7062,16 +7073,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7102,50 +7114,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -7179,26 +7196,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7226,24 +7264,45 @@
           <t>non_idp_NG034002_1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7271,24 +7330,45 @@
           <t>non_idp_NG034002_11</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7316,24 +7396,45 @@
           <t>non_idp_NG034002_12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7361,24 +7462,45 @@
           <t>non_idp_NG034002_13</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7406,24 +7528,45 @@
           <t>non_idp_NG034002_15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7451,24 +7594,45 @@
           <t>non_idp_NG034002_3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7496,24 +7660,45 @@
           <t>non_idp_NG034002_4</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7541,24 +7726,45 @@
           <t>non_idp_NG034002_7</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7586,24 +7792,45 @@
           <t>non_idp_NG034002_9</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7631,24 +7858,29 @@
           <t>non_idp_NG034002_supp10</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7676,24 +7908,29 @@
           <t>non_idp_NG034002_supp2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7721,24 +7958,29 @@
           <t>non_idp_NG034002_supp5</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7766,24 +8008,29 @@
           <t>non_idp_NG034002_supp8</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7811,24 +8058,29 @@
           <t>non_idp_NG034002_supp9</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7858,26 +8110,31 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7907,26 +8164,31 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7956,26 +8218,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8005,26 +8272,31 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>In-camp</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8039,37 +8311,46 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rimawa</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>idp_NG034006_supp1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8084,37 +8365,46 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goronyo</t>
+          <t>Shinaka</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_11</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>idp_NG034006_supp2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8129,7 +8419,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Birjingo</t>
+          <t>Rimawa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8139,27 +8429,44 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_12</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8174,7 +8481,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sabon Gari Dole</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8184,27 +8491,52 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_13</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_11</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Marked accessible per Godwin (STCI) email 2026-09-16: respondents displaced by banditry, currently reside in Kagara IDP Camp (Goronyo LGA) and are reachable there. Overrides the returned workbook's own cell, which said No with no reason given.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8219,7 +8551,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Takakume</t>
+          <t>Birjingo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8229,27 +8561,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_14</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8264,7 +8613,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rimawa</t>
+          <t>Sabon Gari Dole</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8274,27 +8623,44 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_15</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_13</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8309,7 +8675,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rimawa</t>
+          <t>Takakume</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8319,27 +8685,44 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_16</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_14</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8364,27 +8747,44 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_17</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8399,7 +8799,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kwakwazo</t>
+          <t>Rimawa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8409,27 +8809,44 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_3</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_16</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8444,7 +8861,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kojiyo</t>
+          <t>Rimawa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8454,27 +8871,44 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_4</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_17</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8489,7 +8923,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sabon Gari Dole</t>
+          <t>Kwakwazo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8499,27 +8933,44 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_5</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8534,7 +8985,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Giyawa</t>
+          <t>Kojiyo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8544,27 +8995,44 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_6</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_4</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8579,7 +9047,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Goronyo</t>
+          <t>Sabon Gari Dole</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8589,27 +9057,44 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_7</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8624,7 +9109,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Takakume</t>
+          <t>Giyawa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8634,27 +9119,44 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_8</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_6</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8679,27 +9181,44 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG034006_9</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG034006_7</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8709,46 +9228,59 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Takakume</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>idp_NG034005_1</t>
+          <t>non_idp_NG034006_8</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8758,46 +9290,59 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Goronyo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>idp_NG034005_6</t>
+          <t>non_idp_NG034006_9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8822,31 +9367,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>idp_NG034005_supp1</t>
+          <t>idp_NG034005_1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8861,7 +9427,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8871,31 +9437,52 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>idp_NG034005_supp2</t>
+          <t>idp_NG034005_6</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8910,37 +9497,46 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chimola</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_11</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>idp_NG034005_supp1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8960,32 +9556,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_5</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>idp_NG034005_supp2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9010,27 +9615,48 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_6</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_11</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9045,7 +9671,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9055,27 +9681,48 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_7</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9100,27 +9747,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_6</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9135,7 +9803,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Darna Tsolawo</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9145,27 +9813,48 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp11</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_7</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9180,7 +9869,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gidan Kaya</t>
+          <t>Chimola</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9190,27 +9879,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp12</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9225,7 +9919,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Darna Tsolawo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9235,27 +9929,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp13</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp11</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9280,27 +9979,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp14</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp12</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9315,7 +10019,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gidan Kaya</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -9325,27 +10029,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp15</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp13</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9370,27 +10079,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp14</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9405,7 +10119,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Gidan Kaya</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -9415,27 +10129,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp3</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9450,7 +10169,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gwadabawa</t>
+          <t>Gidan Kaya</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -9460,27 +10179,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp4</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9495,7 +10219,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gidan Kaya</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -9505,27 +10229,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp6</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp3</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9540,7 +10269,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Asara</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9550,27 +10279,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG034005_supp9</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034005_supp4</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9580,46 +10314,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Gidan Kaya</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>idp_NG034012_1</t>
+          <t>non_idp_NG034005_supp6</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9629,46 +10364,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Gwadabawa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gandi 1</t>
+          <t>Asara</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>idp_NG034012_12</t>
+          <t>non_idp_NG034005_supp9</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9683,7 +10419,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Goddodi</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9693,31 +10429,36 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>idp_NG034012_4</t>
+          <t>idp_NG034012_1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9732,7 +10473,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9742,31 +10483,36 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>idp_NG034012_6</t>
+          <t>idp_NG034012_12</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>In-host</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9781,37 +10527,46 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rarah</t>
+          <t>Goddodi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_10</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>idp_NG034012_4</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9826,37 +10581,46 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tofa</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_12</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>idp_NG034012_6</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9871,23 +10635,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tsamiya</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_14</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>idp_NG034012_supp1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9895,13 +10663,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9916,23 +10689,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tsamiya</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_15</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>idp_NG034012_supp2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9940,13 +10717,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9966,18 +10748,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_16</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>idp_NG034012_supp3</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9985,13 +10771,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10006,23 +10797,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yarstakuwa</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_17</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>idp_NG034012_supp4</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10030,13 +10825,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10051,23 +10851,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yarstakuwa</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_2</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>idp_NG034012_supp5</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10075,13 +10879,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10096,23 +10905,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maikujera</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_3</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>idp_NG034012_supp6</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10120,13 +10933,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10141,23 +10959,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rabah</t>
+          <t>Gandi 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_4</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>idp_NG034012_supp7</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10165,13 +10987,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10186,7 +11013,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maikujera</t>
+          <t>Rarah</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10196,27 +11023,44 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_5</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_10</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10231,7 +11075,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Goddodi</t>
+          <t>Tofa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10241,27 +11085,44 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_6</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_12</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10276,7 +11137,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Goddodi</t>
+          <t>Tsamiya</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10286,27 +11147,44 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_7</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_14</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10321,7 +11199,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Goddodi</t>
+          <t>Tsamiya</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10331,27 +11209,44 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_8</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_15</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10366,7 +11261,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rarah</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10376,27 +11271,44 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_9</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_16</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10411,7 +11323,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rarah</t>
+          <t>Yarstakuwa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10421,27 +11333,44 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_supp1</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_17</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10456,7 +11385,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tsamiya</t>
+          <t>Yarstakuwa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10466,27 +11395,44 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG034012_supp2</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10496,46 +11442,59 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Maikujera</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>idp_NG034018_10</t>
+          <t>non_idp_NG034012_3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10545,46 +11504,59 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saida Goshe</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>idp_NG034018_15</t>
+          <t>non_idp_NG034012_4</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" s="10" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10594,46 +11566,59 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sanyinna</t>
+          <t>Maikujera</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>idp_NG034018_16</t>
+          <t>non_idp_NG034012_5</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10643,46 +11628,59 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romo Sarki</t>
+          <t>Goddodi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>idp_NG034018_4</t>
+          <t>non_idp_NG034012_6</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" s="10" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10692,46 +11690,59 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sabon Birni</t>
+          <t>Goddodi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>idp_NG034018_supp1</t>
+          <t>non_idp_NG034012_7</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10741,46 +11752,59 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sabon Birni</t>
+          <t>Goddodi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>idp_NG034018_supp2</t>
+          <t>non_idp_NG034012_8</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" s="10" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10790,12 +11814,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bagida</t>
+          <t>Rarah</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10805,27 +11829,44 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_10</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_9</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10835,12 +11876,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Barkeji-Nabaguda</t>
+          <t>Rarah</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10850,27 +11891,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_12</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_supp1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" s="10" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10880,12 +11926,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Rabah</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bagida</t>
+          <t>Tsamiya</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10895,27 +11941,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_13</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034012_supp2</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10930,37 +11981,62 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dogon Daji</t>
+          <t>Tambuwal</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_14</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>idp_NG034018_10</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" s="10" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10975,23 +12051,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Barkeji-Nabaguda</t>
+          <t>Saida Goshe</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_15</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>idp_NG034018_15</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -10999,13 +12079,34 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" s="10" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11025,32 +12126,57 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_16</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>idp_NG034018_16</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" s="10" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11065,37 +12191,62 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saida Goshe</t>
+          <t>Romo Sarki</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_17</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>idp_NG034018_4</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" s="10" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11110,23 +12261,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Faga Alasan</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_5</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>idp_NG034018_supp1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -11134,13 +12289,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" s="10" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11155,37 +12315,46 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_6</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>idp_NG034018_supp2</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" s="10" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11200,37 +12369,46 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romo Sarki</t>
+          <t>Sabon Birni</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_8</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>idp_NG034018_supp4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" s="10" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11245,7 +12423,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tambuwal</t>
+          <t>Bagida</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11255,27 +12433,48 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_9</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034018_10</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" s="10" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11300,27 +12499,48 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_supp1</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034018_12</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" s="10" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11345,27 +12565,48 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_supp3</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034018_13</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" s="10" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11380,7 +12621,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Barkeji-Nabaguda</t>
+          <t>Dogon Daji</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11390,27 +12631,48 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>non_idp_NG034018_supp4</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG034018_14</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" s="10" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11435,45 +12697,662 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>non_idp_NG034018_15</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sanyinna</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_16</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Saida Goshe</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_17</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Faga Alasan</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_5</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_6</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Romo Sarki</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_8</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_9</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp1</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bagida</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp3</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp4</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>non_idp_NG034018_supp5</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" s="10" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11739,13 +13618,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A0AA5DD-F090-40A8-B95D-BD7B2D695844}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{994BDF52-3D0C-42CA-AECB-1907C41E2639}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD99D542-E102-4389-99F7-44CC4DA1D929}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4271BC7-50C9-4D02-B742-ACEBA93D86A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{548F7AC7-E9BB-4C85-9DB5-833132B11E6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91EF7A1B-0CDC-4314-8787-2D1C4F9CD788}"/>
 </file>